--- a/ci-cd-merge-resolver/repoCollector/datasets/HikariCP.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/HikariCP.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -51,6 +51,15 @@
   </si>
   <si>
     <t>70c0e3d96ba8a14efb61e375915027b7346ba49f</t>
+  </si>
+  <si>
+    <t>79c9e5a70985b659bed26e3d307d6e72ad541e89</t>
+  </si>
+  <si>
+    <t>7da729bbe8c02db2e7c4b6bc7b2af09ad6cd4c6c</t>
+  </si>
+  <si>
+    <t>a310df95d71c0e3248efb9322f6a62a19590402d</t>
   </si>
   <si>
     <t>7ec98c3ee21bd5cdbfd3551d46c5fc44a4864f78</t>
@@ -104,7 +113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -150,7 +159,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>4.0</v>
+        <v>52.0</v>
       </c>
       <c r="E2" t="n" s="0">
         <v>1.0</v>
@@ -165,10 +174,10 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>0.003000000026077032</v>
+        <v>0.2680000066757202</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -182,24 +191,56 @@
         <v>15</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>168.0</v>
+        <v>99.0</v>
       </c>
       <c r="E3" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="F3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G3" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H3" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n" s="0">
+        <v>0.20100000500679016</v>
+      </c>
+      <c r="J3" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="D4" t="n" s="0">
+        <v>172.0</v>
+      </c>
+      <c r="E4" t="n" s="0">
         <v>2.0</v>
       </c>
-      <c r="F3" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G3" t="b" s="0">
-        <v>0</v>
-      </c>
-      <c r="H3" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n" s="0">
-        <v>246.01296997070312</v>
-      </c>
-      <c r="J3" t="b" s="0">
+      <c r="F4" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G4" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H4" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n" s="0">
+        <v>208.552001953125</v>
+      </c>
+      <c r="J4" t="b" s="0">
         <v>0</v>
       </c>
     </row>
